--- a/open-world/config/excel/港口收益.xlsx
+++ b/open-world/config/excel/港口收益.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="派遣" sheetId="1" r:id="Rd05b4be9d6224056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="声望" sheetId="2" r:id="Rf61825d6eb694879"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="捐献" sheetId="3" r:id="Re4c47af7dac347c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配方" sheetId="4" r:id="R3d4c4cbe1f8f42b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="5" r:id="Rf696a5d9182148e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" r:id="R4799312e998b494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="派遣" sheetId="1" r:id="R88d398d287dc497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="声望" sheetId="2" r:id="R734f52ace1744414"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="捐献" sheetId="3" r:id="R66e1f46081b84542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配方" sheetId="4" r:id="R7982031b74054cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导出" sheetId="5" r:id="R2e046f9936234a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" r:id="Rf16c46892d2f47bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -667,9 +667,53 @@
         <x:v>{"mist_ore":1.0931174089068827,"mist_herb":1.0931174089068827}</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="1" t="str">
+        <x:v>forge</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="n">
+        <x:v>273.6842105263158</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>{"forge_ore":0.7287449392712552,"forge_herb":0.7287449392712552}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="1" t="str">
+        <x:v>frost</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="n">
+        <x:v>463.1578947368421</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="str">
+        <x:v>{"frost_ore":0.7287449392712552,"frost_herb":0.7287449392712552}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="1" t="str">
+        <x:v>rift</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="n">
+        <x:v>768.4210526315788</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>{"rift_ore":0.7287449392712552,"rift_herb":0.7287449392712552}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="1" t="str">
+        <x:v>dragon</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="n">
+        <x:v>1178.9473684210527</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="str">
+        <x:v>{"dragon_ore":0.7287449392712552,"dragon_herb":0.7287449392712552}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95c3542569934d86"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ff8b9c81db4419f"/>
 </x:worksheet>
 </file>
 
@@ -771,7 +815,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R505bb1f98d554ecf"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08babaa08ab74c4e"/>
 </x:worksheet>
 </file>
 
@@ -841,7 +885,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75b13adbb7834fbc"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b2b03ac869c471c"/>
 </x:worksheet>
 </file>
 
@@ -967,9 +1011,135 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="1" t="str">
+        <x:v>forge-resist</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="1" t="str">
+        <x:v>forge-essence</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="1" t="str">
+        <x:v>frost-resist</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="1" t="str">
+        <x:v>frost-essence</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="1" t="str">
+        <x:v>rift-resist</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="1" t="str">
+        <x:v>rift-essence</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="1" t="str">
+        <x:v>enchant-legend</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="1" t="str">
+        <x:v>dragon-resist</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="1" t="str">
+        <x:v>dragon-essence</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9800f6df9d942a1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc91c0e045d094e3c"/>
 </x:worksheet>
 </file>
 
